--- a/output/full_scan/batch_seq3_2026-10-13.xlsx
+++ b/output/full_scan/batch_seq3_2026-10-13.xlsx
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>69.29139216471539</v>
+        <v>69.29139216235228</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>34.02312803774745</v>
@@ -578,7 +578,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1084288504372096</v>
+        <v>0.1084288504492264</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>63.60397473627656</v>
+        <v>63.6039747803496</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16.51082509981335</v>
+        <v>16.51082512979737</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.867237988066302</v>
@@ -631,7 +631,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0700264988046834</v>
+        <v>0.0700264987445957</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -666,10 +666,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>83.02552027751454</v>
+        <v>83.02552042036079</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>38.19894926784841</v>
+        <v>38.1989492873325</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>6.195798695655023</v>
@@ -684,7 +684,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.451157938629166</v>
+        <v>2.451157937547606</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.38807318813315</v>
+        <v>68.38807319184667</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26.2117966428753</v>
+        <v>26.21179674915575</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.037693914497281</v>
@@ -737,7 +737,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2733905138715294</v>
+        <v>0.273390513895569</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>71.49704681136058</v>
+        <v>71.49704686125945</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.87903901750126</v>
+        <v>18.87903909388753</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>5.239810315812131</v>
@@ -790,7 +790,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.342426388657909</v>
+        <v>1.342426388177226</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>63.09781438864437</v>
+        <v>63.09781446381156</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.35414661361644</v>
+        <v>23.35414686252756</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.796023772144778</v>
@@ -843,7 +843,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1134493698247385</v>
+        <v>0.1134493696084261</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>70.53366619214809</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24.10725351562328</v>
+        <v>24.10725358307993</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.979285052062041</v>
@@ -896,7 +896,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.115927207677898</v>
+        <v>1.115927207798087</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>56.18397213407734</v>
+        <v>56.18397230771132</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>11.63499589000002</v>
+        <v>11.63499600650403</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>1.679839400048698</v>
@@ -949,7 +949,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.0390394458879188</v>
+        <v>0.0390394457437081</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1209.033189609377</v>
+        <v>1209.033189609376</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>160</v>
@@ -984,10 +984,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>68.46686402043636</v>
+        <v>68.46686409662529</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>29.47722847229091</v>
+        <v>29.47722857674495</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.256305807215132</v>
@@ -1002,7 +1002,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0700301964599878</v>
+        <v>0.07003019617155939</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.75105933720813</v>
+        <v>60.75105943977262</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.15290517786041</v>
+        <v>28.15290543700947</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.040644932780717</v>
@@ -1055,7 +1055,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.1581383205400317</v>
+        <v>-0.1581383208044176</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1090,10 +1090,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.82812832316401</v>
+        <v>66.82812828754345</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35.70549611104454</v>
+        <v>35.70549609092367</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.538644008615338</v>
@@ -1108,7 +1108,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.0419440243732325</v>
+        <v>-0.0419440243492024</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.62770066296198</v>
+        <v>63.62770061872207</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>26.40901338304129</v>
+        <v>26.40901368075253</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>2.298992458743057</v>
@@ -1161,7 +1161,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0754578789186859</v>
+        <v>0.0754578791590421</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>73.80020122582744</v>
+        <v>73.80020126804038</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>47.7861843534782</v>
+        <v>47.78618451785601</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2.253073753188332</v>
@@ -1214,7 +1214,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0480177668824839</v>
+        <v>0.0480177668464374</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>63.66109039344738</v>
+        <v>63.66109037394693</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45.99575691419611</v>
+        <v>45.99575679379786</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>3.736572700308938</v>
@@ -1267,7 +1267,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0254177737311454</v>
+        <v>0.0254177738272849</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>70.42942544944428</v>
+        <v>70.42942570314997</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.14698139854066</v>
+        <v>20.1469815386026</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2.282279313498137</v>
@@ -1320,7 +1320,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.8360242678400633</v>
+        <v>0.8360242671190194</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.59440761928131</v>
+        <v>59.59440767121201</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.99515178718565</v>
+        <v>31.9951519198926</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.331960863230314</v>
@@ -1373,7 +1373,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.05491474597041</v>
+        <v>-0.0549147463549717</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>82.99557370534779</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>34.12441520652476</v>
+        <v>34.12441524012216</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>4.708682016059673</v>
@@ -1426,7 +1426,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.3977787113686938</v>
+        <v>0.3977787112352033</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.79281308092423</v>
+        <v>58.7928132164743</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>30.03181427498981</v>
+        <v>30.03181439625473</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1.016161778275838</v>
@@ -1479,7 +1479,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0875326349038739</v>
+        <v>-0.0875326354085981</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.06078390516716</v>
+        <v>60.0607838892795</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>23.51573233556224</v>
+        <v>23.51573243440886</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.575655121598269</v>
@@ -1567,10 +1567,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.49565923968903</v>
+        <v>58.49565929685283</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.25460630535003</v>
+        <v>27.25460635695417</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1.01454540255446</v>
@@ -1585,7 +1585,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0298912609285521</v>
+        <v>0.0298912608083805</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>66.63826591902307</v>
+        <v>66.6382662529237</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.89372002528538</v>
+        <v>23.89372016464942</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>5.118765495503433</v>
@@ -1638,7 +1638,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.119172920136</v>
+        <v>0.1191729198115336</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>65.03114446067235</v>
+        <v>65.03114457640899</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>41.2792796641848</v>
+        <v>41.27927983710208</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.554857105699047</v>
@@ -1691,7 +1691,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5461448796157771</v>
+        <v>0.5461448790149164</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>978.3840173411209</v>
+        <v>978.3840173411212</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>42.9</v>
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.68022523221968</v>
+        <v>51.68022535587849</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>14.44686239040599</v>
+        <v>14.44686258722819</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>4.72382799974418</v>
@@ -1744,7 +1744,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2410383243503386</v>
+        <v>0.2410383242061281</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.1259079548248</v>
+        <v>57.12590807387348</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.28861719585516</v>
+        <v>26.28861744047558</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.5281833688134973</v>
@@ -1797,7 +1797,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.3921630198171106</v>
+        <v>-0.3921630204179702</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.29421844647688</v>
+        <v>53.29421845951558</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>17.44397575956162</v>
+        <v>17.44397578373294</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.427588167129458</v>
@@ -1850,7 +1850,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.589146212168874</v>
+        <v>-1.589146212649681</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>73.41370020275551</v>
+        <v>73.4137001842002</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.09458200265511</v>
+        <v>37.09458210495439</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.643391450268779</v>
@@ -1924,7 +1924,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>932.9192618060404</v>
+        <v>932.91926180604</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>58.6</v>
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>65.86931383423682</v>
+        <v>65.86931388401601</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>41.24449623982443</v>
+        <v>41.24449641731603</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.737908175037216</v>
@@ -1956,7 +1956,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0065166992139342</v>
+        <v>0.0065166991298126</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1991,10 +1991,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>62.36504661677689</v>
+        <v>62.36504672984675</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.02133922768303</v>
+        <v>22.0213392983657</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.273210571640868</v>
@@ -2009,7 +2009,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>4.650001000628526</v>
+        <v>4.650000999426748</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2044,10 +2044,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.12789759496465</v>
+        <v>59.12789801187125</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24.77548494949452</v>
+        <v>24.77548498298473</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>1.287280688369663</v>
@@ -2062,7 +2062,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0839298205422659</v>
+        <v>0.0839298211431193</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>64.10839755805202</v>
+        <v>64.10839757440918</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.56022209067857</v>
+        <v>17.56022218004044</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>2.159997804879469</v>
@@ -2115,7 +2115,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>70.45465912421059</v>
+        <v>70.4546591170008</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>60.79070015532265</v>
+        <v>60.79070030860393</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.17498775183395</v>
+        <v>22.17498808626064</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.403556129065375</v>
@@ -2168,7 +2168,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.1237519497525863</v>
+        <v>-0.1237519520359029</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>63.00656446283288</v>
+        <v>63.0065643054576</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.58953678754787</v>
+        <v>32.5895367479569</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>2.238066567503735</v>
@@ -2221,7 +2221,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.2845713479795195</v>
+        <v>-0.2845713466576209</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>63.75161356010293</v>
+        <v>63.75161359761089</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>38.92763368446943</v>
+        <v>38.92763384494181</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.6975432850653756</v>
@@ -2274,7 +2274,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.09464095423887731</v>
+        <v>-0.0946409542749316</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2309,10 +2309,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>67.83668213780257</v>
+        <v>67.83668215586074</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>35.62553325859614</v>
+        <v>35.62553330379464</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.076579704735581</v>
@@ -2327,7 +2327,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0904603748593454</v>
+        <v>-0.0904603748833743</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2362,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>71.52669041241832</v>
+        <v>71.5266904805311</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26.6758155243018</v>
+        <v>26.6758155794667</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>2.441123954807682</v>
@@ -2380,7 +2380,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.2460074569426219</v>
+        <v>0.2460074568945512</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>63.23145831222705</v>
+        <v>63.23145832160448</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26.49101445253755</v>
+        <v>26.49101453696789</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1.742499618831156</v>
@@ -2468,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.99043006214201</v>
+        <v>55.9904298719383</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30.59570468573745</v>
+        <v>30.59570466350048</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.946459946114739</v>
@@ -2486,7 +2486,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.1664658092953118</v>
+        <v>-0.1664658093193429</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>67.51732295525724</v>
+        <v>67.51732305898841</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>34.36820862462987</v>
+        <v>34.36820872067031</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>1.251768995104488</v>
@@ -2539,7 +2539,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>2.879519999922064</v>
+        <v>2.879519997278252</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.3908435895143</v>
+        <v>57.39084372923738</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.46246555031127</v>
+        <v>22.46246591026316</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.8903044621865959</v>
@@ -2592,7 +2592,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.9197555334670796</v>
+        <v>0.919755532505708</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2627,10 +2627,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>62.07538740290171</v>
+        <v>62.07538742539632</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>52.14451537047079</v>
+        <v>52.14451537495955</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.8446518913290251</v>
@@ -2645,7 +2645,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.189866395203754</v>
+        <v>1.189866395023486</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2680,10 +2680,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>65.0269967153108</v>
+        <v>65.02699672728829</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>17.6421582434638</v>
+        <v>17.64215835965382</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.7372810314114249</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>60.22387849931746</v>
+        <v>60.22387852448783</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.60965951896032</v>
+        <v>28.60965957330728</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1.013475738688761</v>
@@ -2751,7 +2751,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.383460986457901</v>
+        <v>1.383460986289648</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2786,10 +2786,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>59.22120212023179</v>
+        <v>59.22120196570056</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30.2196407106009</v>
+        <v>30.21964068408704</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.9884573557304774</v>
@@ -2804,7 +2804,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0222962794490922</v>
+        <v>0.0222962794250572</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>58.98170360733149</v>
+        <v>58.98170364558548</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>33.22444184380183</v>
+        <v>33.22444190484778</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.7944832588473056</v>
@@ -2857,7 +2857,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.2685458740330142</v>
+        <v>-0.2685458740690725</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>812.4639029665591</v>
+        <v>812.463902966559</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>50.9</v>
@@ -2892,10 +2892,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.17229495112982</v>
+        <v>58.17229497568282</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.60373614966677</v>
+        <v>24.60373621816992</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.177672974448861</v>
@@ -2910,7 +2910,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.013059922583312</v>
+        <v>-0.0130599226914646</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2945,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>61.27330782712242</v>
+        <v>61.27330805710207</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.95797053683204</v>
+        <v>24.95797053920329</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.216848824013332</v>
@@ -2963,7 +2963,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0526035676236402</v>
+        <v>0.0526035676116236</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2998,10 +2998,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.70686047427903</v>
+        <v>54.70686048988513</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8.166487563090525</v>
+        <v>8.166487744218895</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.6978365631087871</v>
@@ -3016,7 +3016,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1408468225694098</v>
+        <v>0.14084682239778</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>62.97507081510271</v>
+        <v>62.97507083454561</v>
       </c>
       <c r="I49" s="2" t="n">
         <v>33.02566458021693</v>
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.80234671783715</v>
+        <v>53.80234664760839</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>29.62324457516991</v>
+        <v>29.62324460949349</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>1.141399497330858</v>
@@ -3122,7 +3122,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.1720159196882748</v>
+        <v>-0.1720159197123065</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>789.7709077920825</v>
+        <v>789.770907792082</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>235.5</v>
@@ -3157,10 +3157,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>56.05048303051633</v>
+        <v>56.05048302913846</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.9615259331106</v>
+        <v>18.9615260331</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>2.691204520864817</v>
@@ -3175,7 +3175,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>3.763282807332057</v>
+        <v>3.763282807284011</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>64.09497921803813</v>
+        <v>64.09497923146812</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>43.78196566074695</v>
+        <v>43.78196584732103</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.5595533095262361</v>
@@ -3228,7 +3228,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.2791217983320315</v>
+        <v>0.2791217982719449</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>55.38768000796384</v>
+        <v>55.38767998912387</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.91962423958121</v>
+        <v>23.9196242492743</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.8368609601807137</v>
@@ -3281,7 +3281,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.06437403929291841</v>
+        <v>-0.0643740393289723</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>758.4028049013374</v>
+        <v>758.4028049013375</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>52</v>
@@ -3316,10 +3316,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>66.34159037796341</v>
+        <v>66.34159044133978</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>35.00062881670229</v>
+        <v>35.00062894735127</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.7319961296938217</v>
@@ -3334,7 +3334,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.3812605725951479</v>
+        <v>0.3812605724389224</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>62.114356099709</v>
+        <v>62.11435621200816</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>33.85165903444443</v>
+        <v>33.85165912821468</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>1.839698393598185</v>
@@ -3387,7 +3387,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2310929541372164</v>
+        <v>0.2310929538728314</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>64.17278365608104</v>
+        <v>64.17278367721384</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>39.88097641539636</v>
+        <v>39.88097640050468</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.8817019841861841</v>
@@ -3440,7 +3440,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.2277271167099355</v>
+        <v>-0.2277271167820389</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3475,10 +3475,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>59.6817390656935</v>
+        <v>59.68173933622519</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>39.0482450266225</v>
+        <v>39.04824444672778</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>3.448151378147453</v>
@@ -3493,7 +3493,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0340294753268786</v>
+        <v>-0.0340294748279531</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>55.10466277535317</v>
+        <v>55.10466287442625</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.51273727241242</v>
+        <v>20.51273730419435</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>2.286059573344096</v>
@@ -3546,7 +3546,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.5917907439297785</v>
+        <v>0.5917907436894303</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3581,10 +3581,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.78821581449198</v>
+        <v>52.7882158373295</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>26.2864614594452</v>
+        <v>26.28646152696395</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.544077140781911</v>
@@ -3599,7 +3599,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0443006632465942</v>
+        <v>-0.0443006632514011</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>47.28622515719059</v>
+        <v>47.28622517518659</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>32.95125500578631</v>
+        <v>32.95125515593465</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.95158603245038</v>
@@ -3652,7 +3652,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1048561121805869</v>
+        <v>-0.1048561121565508</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3687,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>63.53689592626375</v>
+        <v>63.53689623936013</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.06322326351029</v>
+        <v>20.06322340399624</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.054835594722561</v>
@@ -3705,7 +3705,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.07229225691786161</v>
+        <v>0.0722922567976904</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>695.5065101194841</v>
+        <v>695.506510119484</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>47.2</v>
@@ -3740,10 +3740,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.61628303665684</v>
+        <v>53.61628364653576</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>25.27967429553399</v>
+        <v>25.27967392010053</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.9356168623196148</v>
@@ -3758,7 +3758,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.4672160138247693</v>
+        <v>0.4672160130316281</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3793,10 +3793,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>64.51923205005544</v>
+        <v>64.51923223633081</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>40.42210659111942</v>
+        <v>40.42210674388139</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>1.891755219782607</v>
@@ -3811,7 +3811,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.173014657258317</v>
+        <v>0.1730146571621811</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>53.58332296869249</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>28.62000471255688</v>
+        <v>28.6200047051137</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.4079036707710561</v>
@@ -3864,7 +3864,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0143243073441599</v>
+        <v>-0.0143243073681954</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>674.4081614680844</v>
+        <v>674.4081614680828</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>8.52</v>
@@ -3899,10 +3899,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>57.80337847868768</v>
+        <v>57.80337914081642</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.49004197711465</v>
+        <v>23.49004219212942</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>1.942572260768288</v>
@@ -3917,7 +3917,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0612016352496015</v>
+        <v>0.0612016349972389</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>668.5376157026684</v>
+        <v>668.5376157026685</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>32</v>
@@ -3952,10 +3952,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>61.6494029604639</v>
+        <v>61.64940311014065</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16.41876713301552</v>
+        <v>16.41876710711087</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>1.428458265400626</v>
@@ -3970,7 +3970,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1561433795549481</v>
+        <v>0.156143379458808</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>58.87516531120367</v>
+        <v>58.8751653150002</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>25.63018343834281</v>
+        <v>25.63018342863503</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.99801386872152</v>
@@ -4023,7 +4023,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1939388367771549</v>
+        <v>-0.1939388367651374</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.92806385964326</v>
+        <v>52.92806386061044</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>31.01957667524819</v>
+        <v>31.01957670771009</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.9136995476229776</v>
@@ -4076,7 +4076,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.212526001947062</v>
+        <v>-1.212526001971163</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4111,10 +4111,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>52.95231928769762</v>
+        <v>52.95231962056258</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>9.371929370773383</v>
+        <v>9.371929482097563</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1.089037997665945</v>
@@ -4129,7 +4129,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0383904950945903</v>
+        <v>0.0383904950224858</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>48.62938158554808</v>
+        <v>48.62938159322827</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>9.764686914187893</v>
+        <v>9.764686887133507</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>1.077066073444824</v>
@@ -4182,7 +4182,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0348363722063274</v>
+        <v>0.034836372194314</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>658.7756211714145</v>
+        <v>658.7756211714218</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>38.9</v>
@@ -4217,10 +4217,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.78264256719557</v>
+        <v>51.78264260714251</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>24.294895686926</v>
+        <v>24.29489581762774</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.916572286969042</v>
@@ -4235,7 +4235,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1375796239594152</v>
+        <v>0.1375796236710099</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4270,10 +4270,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>54.95087874533386</v>
+        <v>54.95087891823754</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.2147325790045</v>
+        <v>17.2147326875583</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>1.021151673098158</v>
@@ -4288,7 +4288,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.5231397559863398</v>
+        <v>0.5231397554816186</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4323,10 +4323,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>36.63867605405611</v>
+        <v>36.6386760693978</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>29.38518978465948</v>
+        <v>29.38518979417067</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.5268312613020296</v>
@@ -4341,7 +4341,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0752820871577675</v>
+        <v>-0.0752820872178581</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>649.915741504737</v>
+        <v>649.9157415047367</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>210</v>
@@ -4376,10 +4376,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>56.2255681054704</v>
+        <v>56.22556823223145</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.25456700343641</v>
+        <v>18.25456713626009</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1.261314468593549</v>
@@ -4394,7 +4394,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>2.963320330192176</v>
+        <v>2.963320329831637</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4429,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.24395447721472</v>
+        <v>46.24395454546935</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>26.96677316873149</v>
+        <v>26.96677324732613</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>1.233103590731528</v>
@@ -4447,7 +4447,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.5238462972782774</v>
+        <v>0.5238462970379378</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>634.155892300123</v>
+        <v>634.1558923001227</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>183.5</v>
@@ -4482,10 +4482,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>54.87808427333654</v>
+        <v>54.87808439092228</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17.68027894724317</v>
+        <v>17.68027896216338</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.7193001748046246</v>
@@ -4500,7 +4500,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.502122926728601</v>
+        <v>0.5021229256470746</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4535,10 +4535,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>54.29777486141143</v>
+        <v>54.29777487210541</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>27.47992905469998</v>
+        <v>27.47992918759858</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1.122077153010684</v>
@@ -4553,7 +4553,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>4.353431432344237</v>
+        <v>4.353431431022372</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>633.8477659791912</v>
+        <v>633.8477659791913</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>20.25</v>
@@ -4588,10 +4588,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.72994207317164</v>
+        <v>45.72994228220532</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>25.98345732489131</v>
+        <v>25.98345725349319</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.7268144487556248</v>
@@ -4606,7 +4606,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0047130175066335</v>
+        <v>-0.0047130175667194</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.79267376282146</v>
+        <v>52.79267383464514</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>24.44303748216961</v>
+        <v>24.44303748078215</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>1.09417809663695</v>
@@ -4694,10 +4694,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.75545997063863</v>
+        <v>51.75546001018817</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.26891477870214</v>
+        <v>12.26891482364132</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.9782599944275286</v>
@@ -4712,7 +4712,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.1164401421624449</v>
+        <v>-0.1164401420663043</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4747,10 +4747,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.51564385908969</v>
+        <v>45.51564391545727</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>32.74801078374296</v>
+        <v>32.74801104028889</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>1.230459545246788</v>
@@ -4765,7 +4765,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-8.464650463507763</v>
+        <v>-8.464650466391941</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>611.9433037690565</v>
+        <v>611.9433037690563</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>17.4</v>
@@ -4800,10 +4800,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>54.37406961918629</v>
+        <v>54.37406962726172</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>6.597949257441038</v>
+        <v>6.597949287095842</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1.765588676691287</v>
@@ -4818,7 +4818,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1.472920132513152</v>
+        <v>1.472920132356927</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>58.74788500572549</v>
+        <v>58.74788496236918</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>21.46493524605309</v>
+        <v>21.46493533685467</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.9739064404711124</v>
@@ -4871,7 +4871,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0268302935415814</v>
+        <v>-0.0268302935536001</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>593.6529336111375</v>
+        <v>593.6529336111374</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>22</v>
@@ -4906,10 +4906,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.54050961954563</v>
+        <v>49.54050964410502</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.58093100991947</v>
+        <v>18.58093107396771</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>1.019974823646771</v>
@@ -4924,7 +4924,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0191756796695184</v>
+        <v>-0.0191756796334677</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4959,10 +4959,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.75590016901417</v>
+        <v>48.7559001963551</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>24.95885961228106</v>
+        <v>24.95885965270548</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.4367335142127022</v>
@@ -4977,7 +4977,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.806374923288387</v>
+        <v>-0.8063749234325952</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5012,10 +5012,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>53.17248259132197</v>
+        <v>53.17248264720497</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>23.47497893158391</v>
+        <v>23.47497907279666</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.5327823463282223</v>
@@ -5030,7 +5030,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.052491801140261</v>
+        <v>-0.0524918011763145</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5065,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.46268904988412</v>
+        <v>43.46268909871493</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>9.691154977615607</v>
+        <v>9.691154977615604</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.926730144024342</v>
@@ -5083,7 +5083,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.2136456624159306</v>
+        <v>0.2136456623678592</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5118,10 +5118,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.50738352098333</v>
+        <v>46.50738337511506</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>27.06074461080077</v>
+        <v>27.0607444941909</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.8883609448179982</v>
@@ -5136,7 +5136,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.486951044109122</v>
+        <v>-1.486951042787225</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5171,10 +5171,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>54.96834339644453</v>
+        <v>54.96834344874099</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>28.16162530569728</v>
+        <v>28.16162534223291</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.9951142069700448</v>
@@ -5189,7 +5189,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0057959535303062</v>
+        <v>0.0057959535543425</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5224,10 +5224,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>65.79675234853183</v>
+        <v>65.79675233814217</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>52.53742190341919</v>
+        <v>52.5374219419565</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.58654326668666</v>
@@ -5277,10 +5277,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.90755148517447</v>
+        <v>43.90755145563576</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>22.75376694894921</v>
+        <v>22.75376693494972</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.629573688422782</v>
@@ -5295,7 +5295,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.3816170849117524</v>
+        <v>-0.3816170849357891</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>53.92238081883049</v>
+        <v>53.92238100680409</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>27.6526929835418</v>
+        <v>27.65269305587702</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>1.172068733058047</v>
@@ -5348,7 +5348,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.8816408746617723</v>
+        <v>0.8816408727390022</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>59.85586065128484</v>
+        <v>59.85586066754868</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>32.8166722257995</v>
+        <v>32.81667231013455</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.922092774950998</v>
@@ -5401,7 +5401,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>1.437209430595431</v>
+        <v>1.43720942985037</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>570.2350700879206</v>
+        <v>570.2350700879205</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>22.35</v>
@@ -5436,10 +5436,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>55.67056634596676</v>
+        <v>55.67056643371406</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>29.02517132388411</v>
+        <v>29.02517134195915</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.6575735255994509</v>
@@ -5454,7 +5454,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0087895292796121</v>
+        <v>0.008789529219525799</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>52.31102112827596</v>
+        <v>52.31102130793792</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>21.1587565742227</v>
+        <v>21.15875660547146</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.3283412947525022</v>
@@ -5528,7 +5528,7 @@
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>560.9032840860484</v>
+        <v>560.9032840860483</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>33.15</v>
@@ -5542,10 +5542,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.02868249354607</v>
+        <v>50.02868254379123</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>4.573158872591512</v>
+        <v>4.573159029277141</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.4786612136038578</v>
@@ -5595,10 +5595,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>42.63704827381331</v>
+        <v>42.63704816577834</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>6.562979736649131</v>
+        <v>6.562979826022166</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>1.167716593806448</v>
@@ -5613,7 +5613,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.2915247067063546</v>
+        <v>0.2915247071870537</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5648,10 +5648,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.70088049844929</v>
+        <v>47.70088089434897</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>28.55641711368901</v>
+        <v>28.55641706633889</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.6931978585327911</v>
@@ -5666,7 +5666,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0558478582274721</v>
+        <v>0.0558478580592294</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>545.8220815040116</v>
+        <v>545.8220815040119</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>317.5</v>
@@ -5701,10 +5701,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.15131965793575</v>
+        <v>49.15131963472135</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.35222319920131</v>
+        <v>15.35222316468624</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>1.206689452514291</v>
@@ -5719,7 +5719,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.6419067711903268</v>
+        <v>0.6419067691473928</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5754,10 +5754,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>48.67557781374051</v>
+        <v>48.67557784392638</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>50.72126847749713</v>
+        <v>50.7212684907159</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.2843302227561781</v>
@@ -5772,7 +5772,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-2.956345106181796</v>
+        <v>-2.956345106878793</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>544.8221487850194</v>
+        <v>544.8221487850193</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>4525</v>
@@ -5807,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.09319978933643</v>
+        <v>45.09319981004673</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>28.08919810710204</v>
+        <v>28.08919830088658</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>1.014437458562261</v>
@@ -5825,7 +5825,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-80.82943744113896</v>
+        <v>-80.82943744955097</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>42.15640687665977</v>
+        <v>42.15640698910821</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>9.701237173013771</v>
+        <v>9.701237324557979</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>1.578472062461915</v>
@@ -5878,7 +5878,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.5040290945985222</v>
+        <v>-0.5040290951272708</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>536.6408282948108</v>
+        <v>536.6408282948099</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>11.85</v>
@@ -5913,10 +5913,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.21599937184531</v>
+        <v>46.21599947487196</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>21.76452895091488</v>
+        <v>21.76452898465683</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.9755005793450572</v>
@@ -5931,7 +5931,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.009914017969313099</v>
+        <v>0.009914017921241599</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>532.7069264552348</v>
+        <v>532.7069264552389</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>14.4</v>
@@ -5966,10 +5966,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>52.37145034049279</v>
+        <v>52.37145070621182</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.26679140924648</v>
+        <v>24.26679138984909</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.6148245098791297</v>
@@ -5984,7 +5984,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0048266011905618</v>
+        <v>-0.0048266013828394</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6019,10 +6019,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.20809723893287</v>
+        <v>46.20809742619905</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>20.34831469825738</v>
+        <v>20.3483148209711</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.8189786766705556</v>
@@ -6037,7 +6037,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0661949840826523</v>
+        <v>-0.0661949841787912</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>528.2399175875656</v>
+        <v>528.239917587566</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>125</v>
@@ -6072,10 +6072,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>49.71579304211692</v>
+        <v>49.71579305998052</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.16961495351628</v>
+        <v>14.16961494185017</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.208201728313517</v>
@@ -6090,7 +6090,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>1.177160018131344</v>
+        <v>1.177160017927059</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>525.6465424831356</v>
+        <v>525.6465424831365</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>18.75</v>
@@ -6125,10 +6125,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.38751036636261</v>
+        <v>51.38751058603105</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>25.52775777937892</v>
+        <v>25.52775765581985</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.7948397324577715</v>
@@ -6143,7 +6143,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0608161542853088</v>
+        <v>0.0608161540810153</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>52.40720651128005</v>
+        <v>52.40720654336248</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>26.29794141513909</v>
+        <v>26.29794144929758</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.7340249805850955</v>
@@ -6196,7 +6196,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.5309399898236198</v>
+        <v>0.5309399897034492</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>524.2314684810896</v>
+        <v>524.2314684810892</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>64</v>
@@ -6231,10 +6231,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>53.60808634334651</v>
+        <v>53.60808646669064</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>8.451587223234259</v>
+        <v>8.4515872159606</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.6184977706642277</v>
@@ -6284,10 +6284,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>48.61752191849732</v>
+        <v>48.61752197997802</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.76152937114039</v>
+        <v>17.76152942160853</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>2.492958346961472</v>
@@ -6302,7 +6302,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.6207005653889685</v>
+        <v>-0.6207005659417689</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6337,10 +6337,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.51619551135362</v>
+        <v>50.51619593907717</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.41295776178804</v>
+        <v>10.41295814008563</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.6959926523140394</v>
@@ -6355,7 +6355,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0184988121603615</v>
+        <v>0.0184988119560687</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.21303946389818</v>
+        <v>47.21303953165013</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>20.92329975700728</v>
+        <v>20.92329990889962</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>1.011184635154054</v>
@@ -6408,7 +6408,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1565832903549484</v>
+        <v>-0.1565832907875552</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>511.3005494027264</v>
+        <v>511.3005494027265</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>12.2</v>
@@ -6443,10 +6443,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.62437430821171</v>
+        <v>48.6243745243836</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.83894934785579</v>
+        <v>16.83894943062484</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>5.435938273232357</v>
@@ -6461,7 +6461,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0224526184503836</v>
+        <v>0.0224526184383665</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>56.35102128528315</v>
+        <v>56.35102159440731</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.19281070682092</v>
+        <v>15.19281079262982</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.8861872367243486</v>
@@ -6514,7 +6514,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0381038873775623</v>
+        <v>0.0381038873054598</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6549,10 +6549,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>52.85520697247453</v>
+        <v>52.85520704726235</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.6946907137649</v>
+        <v>14.69469067149606</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.9116551111000548</v>
@@ -6567,7 +6567,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1533927699644434</v>
+        <v>0.1533927700605877</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6602,10 +6602,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>52.14467120694278</v>
+        <v>52.14467125061746</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>21.06783476569241</v>
+        <v>21.06783487031751</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.7341854847967717</v>
@@ -6620,7 +6620,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.08549446047747571</v>
+        <v>-0.0854944605015107</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>49.58151898552022</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10.07443249879466</v>
+        <v>10.07443255193295</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.390109309258515</v>
@@ -6694,7 +6694,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>498.6996421506215</v>
+        <v>498.6996421506219</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>20.15</v>
@@ -6708,10 +6708,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.39043760265297</v>
+        <v>43.39043778361</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.20323610170812</v>
+        <v>14.20323608105218</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.9789676681940472</v>
@@ -6726,7 +6726,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0240597638076693</v>
+        <v>0.0240597637475816</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6761,10 +6761,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>42.90534657815427</v>
+        <v>42.90534673856306</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.32906671219341</v>
+        <v>17.32906669241111</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.3094268465939707</v>
@@ -6779,7 +6779,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0036880195190291</v>
+        <v>0.0036880195094157</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6814,10 +6814,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>46.70171255509965</v>
+        <v>46.70171250755839</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>31.58265518879318</v>
+        <v>31.58265516376606</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.5781055786538412</v>
@@ -6832,7 +6832,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-1.526500327686779</v>
+        <v>-1.526500327037853</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6867,10 +6867,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>56.92847249490615</v>
+        <v>56.92847262815386</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>19.02434642068456</v>
+        <v>19.02434636181065</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.9982056910377456</v>
@@ -6885,7 +6885,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.057949857806619</v>
+        <v>0.0579498577585502</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>50.46816659775958</v>
+        <v>50.46816688425615</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>16.94431270144142</v>
+        <v>16.94431277032711</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.9939264010935038</v>
@@ -6938,7 +6938,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.008599893994069499</v>
+        <v>0.0085998938859197</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>484.2251329229869</v>
+        <v>484.225132922987</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>55.9</v>
@@ -6973,10 +6973,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>54.48533711141405</v>
+        <v>54.48533724356601</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>35.55563855772279</v>
+        <v>35.55563860472918</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5634307070538357</v>
@@ -6991,7 +6991,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.479607654032367</v>
+        <v>0.4796076536718485</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>480.4077804577585</v>
+        <v>480.4077804577583</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>34.4</v>
@@ -7026,10 +7026,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>52.64865580098668</v>
+        <v>52.64865589839102</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>16.8692890026149</v>
+        <v>16.8692890099594</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.9730559196439376</v>
@@ -7044,7 +7044,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0413425529221397</v>
+        <v>0.0413425528139829</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>479.8326510100103</v>
+        <v>479.8326510100133</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>38.8</v>
@@ -7079,10 +7079,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>51.83683509352108</v>
+        <v>51.83683591785488</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>16.64065113516744</v>
+        <v>16.64065114814933</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>1.489921034507855</v>
@@ -7097,7 +7097,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.1728209323338345</v>
+        <v>0.1728209320694573</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>479.7235504417768</v>
+        <v>479.7235504417769</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>176</v>
@@ -7135,7 +7135,7 @@
         <v>45.57650583780112</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>16.01848980604668</v>
+        <v>16.01848983773021</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>1.347735874094869</v>
@@ -7171,7 +7171,7 @@
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>476.3902178788491</v>
+        <v>476.3902178788489</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>242</v>
@@ -7185,10 +7185,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>34.76940219097361</v>
+        <v>34.76940223677339</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>16.26714752741565</v>
+        <v>16.26714763704395</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>1.261447365773422</v>
@@ -7203,7 +7203,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-4.810144420010768</v>
+        <v>-4.810144420323157</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>475.9888648654062</v>
+        <v>475.988864865406</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>38.7</v>
@@ -7238,10 +7238,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>47.63376970792935</v>
+        <v>47.63377013080425</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>17.05784932221631</v>
+        <v>17.057849541551</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>1.586722600585063</v>
@@ -7256,7 +7256,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0136682930749935</v>
+        <v>-0.0136682932432344</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>51.54262106078721</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>13.5076064916171</v>
+        <v>13.50760645619682</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.5794693167665452</v>
@@ -7309,7 +7309,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0503993963824679</v>
+        <v>0.0503993964648491</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>32.08853660188488</v>
+        <v>32.08853665267935</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>31.41640113650433</v>
+        <v>31.41640119053585</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.8656694990533786</v>
@@ -7383,7 +7383,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>469.5398238777884</v>
+        <v>469.5398238777883</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>143.5</v>
@@ -7397,10 +7397,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>48.44386714399085</v>
+        <v>48.44386721183905</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>8.648082903274011</v>
+        <v>8.64808301133688</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>1.130446775660155</v>
@@ -7415,7 +7415,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.1781225498007554</v>
+        <v>0.1781225501612517</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7450,10 +7450,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>52.89118267381154</v>
+        <v>52.89118277454469</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>14.51132049325921</v>
+        <v>14.51132052072524</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>1.37813341325658</v>
@@ -7468,7 +7468,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.0036797051779145</v>
+        <v>0.0036797051538803</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>46.75085508920127</v>
+        <v>46.75085512278784</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>18.09392197922264</v>
+        <v>18.09392208675201</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.7663204978230522</v>
@@ -7521,7 +7521,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-1.086888860223528</v>
+        <v>-1.086888860968606</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>38.81387101981819</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>34.65931002884592</v>
+        <v>34.65930991650139</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.6337987255271748</v>
@@ -7574,7 +7574,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.0167663664975794</v>
+        <v>0.0167663665095966</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>462.8627997227588</v>
+        <v>462.8627997227584</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>40.5</v>
@@ -7609,10 +7609,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>44.0245935064383</v>
+        <v>44.0245943719268</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>27.02240156492208</v>
+        <v>27.02240165688113</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.6147736936601348</v>
@@ -7627,7 +7627,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.0986950537772518</v>
+        <v>-0.0986950542819761</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7662,10 +7662,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>47.91790574485014</v>
+        <v>47.9179056976423</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>12.76263766078936</v>
+        <v>12.76263771544709</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.8168678572057415</v>
@@ -7680,7 +7680,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.0019783277029611</v>
+        <v>0.0019783277269918</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7715,10 +7715,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>43.90859379155633</v>
+        <v>43.90859389335512</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>9.133162378095562</v>
+        <v>9.133162230198309</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.8940546137254246</v>
@@ -7733,7 +7733,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.07977370000180491</v>
+        <v>-0.0797737001700442</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7768,10 +7768,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>45.61094959120621</v>
+        <v>45.61094934586902</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>39.4827367548478</v>
+        <v>39.48273679843818</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.35223228782335</v>
@@ -7786,7 +7786,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.3515523148113649</v>
+        <v>-0.3515523144147958</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7821,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>48.33717474745794</v>
+        <v>48.33717500203005</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>15.5783839367888</v>
+        <v>15.57838413254186</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.8224877269635047</v>
@@ -7839,7 +7839,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.1270535088616021</v>
+        <v>0.1270535079002084</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7874,10 +7874,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>46.17514527752665</v>
+        <v>46.17514529280024</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>16.66135037014929</v>
+        <v>16.6613505655064</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>1.390132625620696</v>
@@ -7892,7 +7892,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>1.953304779079737</v>
+        <v>1.953304771508577</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7927,10 +7927,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>48.0368481796741</v>
+        <v>48.0368482559429</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>15.23863871033452</v>
+        <v>15.23863890012469</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.5428331997342359</v>
@@ -7945,7 +7945,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.3292122145546405</v>
+        <v>-0.3292122147453376</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7980,10 +7980,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>46.54713126729565</v>
+        <v>46.54713132486931</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>14.49624768170552</v>
+        <v>14.49624771443436</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0.7010429476961417</v>
@@ -7998,7 +7998,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.0164473206529142</v>
+        <v>-0.016447320664932</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8033,10 +8033,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>44.32115323240836</v>
+        <v>44.32115330590874</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>11.11414158199156</v>
+        <v>11.11414157002638</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>1.646673091731523</v>
@@ -8051,7 +8051,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.0060284300225035</v>
+        <v>-0.0060284300465366</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8086,10 +8086,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>40.76365197565515</v>
+        <v>40.76365201177647</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>20.92365273079639</v>
+        <v>20.92365275546976</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.9767636059978942</v>
@@ -8104,7 +8104,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.0187060586634724</v>
+        <v>0.0187060586514552</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8139,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>49.9309461739013</v>
+        <v>49.93094625989556</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>13.41395414604491</v>
+        <v>13.41395428824242</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>1.483522451296345</v>
@@ -8157,7 +8157,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>3.762863262453696</v>
+        <v>3.762863261131741</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8192,10 +8192,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>53.85377834492696</v>
+        <v>53.85377837876718</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>46.88129954665649</v>
+        <v>46.88129959432806</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.2715440339322441</v>
@@ -8231,7 +8231,7 @@
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>436.2868318651663</v>
+        <v>436.2868318651664</v>
       </c>
       <c r="E147" s="2" t="n">
         <v>22.3</v>
@@ -8245,10 +8245,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>30.96859747084609</v>
+        <v>30.96859815941504</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>29.79630300537886</v>
+        <v>29.79630314955766</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>1.709716754808011</v>
@@ -8263,7 +8263,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.0180108195061675</v>
+        <v>0.0180108192057395</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>433.6323135370843</v>
+        <v>433.6323135370841</v>
       </c>
       <c r="E148" s="2" t="n">
         <v>53</v>
@@ -8298,10 +8298,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>47.23209674227292</v>
+        <v>47.2320970225929</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>23.17720294690928</v>
+        <v>23.17720315972217</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.4464324499527178</v>
@@ -8316,7 +8316,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.1395630893602724</v>
+        <v>-0.1395630896246575</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>43.60022425220878</v>
+        <v>43.60022428290312</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>20.31595395113791</v>
+        <v>20.31595401080348</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>1.540262414381549</v>
@@ -8390,7 +8390,7 @@
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>432.119111164244</v>
+        <v>432.1191111642441</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>158</v>
@@ -8404,10 +8404,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>52.71972354332782</v>
+        <v>52.71972360083711</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>17.11633686663184</v>
+        <v>17.11633689750637</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>0.6892802218034527</v>
@@ -8422,7 +8422,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-0.4896106048327143</v>
+        <v>-0.4896106051932442</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8432,41 +8432,41 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>2809</v>
+        <v>3114</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>京城銀</t>
+          <t>好德</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>430.3784355717419</v>
+        <v>428.6560992769791</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>56.6</v>
+        <v>37.55</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G151" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>59.22352803190854</v>
+        <v>55.89863450581424</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v/>
+        <v>34.23628659308543</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>6.141559236203543</v>
+        <v>0.5430452623458463</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L151" s="2" t="n">
         <v>0</v>
@@ -8475,31 +8475,31 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.0575987418509647</v>
+        <v>0.4767795558969925</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>3114</v>
+        <v>3017</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>好德</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>428.6560992769791</v>
+        <v>427.561309070638</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>37.55</v>
+        <v>3280</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -8510,49 +8510,49 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>55.89863450980908</v>
+        <v>46.75095164998663</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>34.23628654943045</v>
+        <v>13.19647463181398</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.5430452623458463</v>
+        <v>0.9297564976286096</v>
       </c>
       <c r="K152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L152" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M152" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.4767795558729599</v>
+        <v>-31.95147719038338</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>3017</v>
+        <v>3090</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>427.561309070638</v>
+        <v>426.1305211945443</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>3280</v>
+        <v>167</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8563,13 +8563,13 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>46.75095158163352</v>
+        <v>47.62759255287871</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>13.19647454806638</v>
+        <v>13.26707978133142</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.9297564976286096</v>
+        <v>1.216659039586636</v>
       </c>
       <c r="K153" s="2" t="n">
         <v>0</v>
@@ -8581,31 +8581,31 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-31.95147717476101</v>
+        <v>0.8691204288513353</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>3090</v>
+        <v>3122</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>笙泉</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>426.1305211945443</v>
+        <v>417.0162420990853</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>167</v>
+        <v>23.75</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>47.62759251702427</v>
+        <v>43.66583588763211</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>13.26707962568619</v>
+        <v>11.5741740880475</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1.216659039586636</v>
+        <v>1.428048787480862</v>
       </c>
       <c r="K154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>0.8691204290916679</v>
+        <v>0.036092512912396</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>3122</v>
+        <v>3060</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>笙泉</t>
+          <t>銘異</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>417.016242099087</v>
+        <v>414.9905182755654</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>23.75</v>
+        <v>27.65</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -8669,13 +8669,13 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>43.66583582237903</v>
+        <v>49.27777773147504</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>11.5741739624559</v>
+        <v>23.97528829115164</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>1.428048787480862</v>
+        <v>1.025407975188494</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>0</v>
@@ -8687,31 +8687,31 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.0360925129244108</v>
+        <v>0.1449994328044337</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>3060</v>
+        <v>2911</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>銘異</t>
+          <t>麗嬰房</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>414.9905182755654</v>
+        <v>410.6817278904842</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>27.65</v>
+        <v>5.89</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8722,16 +8722,16 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>49.27777757124697</v>
+        <v>35.20142817406646</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>23.97528830279644</v>
+        <v>13.28427814323174</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>1.025407975188494</v>
+        <v>1.458639472675545</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L156" s="2" t="n">
         <v>0</v>
@@ -8740,31 +8740,31 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>0.1449994329366219</v>
+        <v>-0.0006946647553164</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>2911</v>
+        <v>2913</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>麗嬰房</t>
+          <t>農林</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>410.6817278904842</v>
+        <v>407.1784387587693</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>5.89</v>
+        <v>11</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -8775,16 +8775,16 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>35.20142821266438</v>
+        <v>49.14408127988249</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>13.28427806685939</v>
+        <v>19.95028544984488</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>1.458639472675545</v>
+        <v>1.219714281949419</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L157" s="2" t="n">
         <v>0</v>
@@ -8793,31 +8793,31 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-0.0006946647481054</v>
+        <v>-0.004362902083176</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>2913</v>
+        <v>3004</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>農林</t>
+          <t>豐達科</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>407.1784387587693</v>
+        <v>404.9333642784369</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -8828,16 +8828,16 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>49.14408109199137</v>
+        <v>48.88690699652074</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>19.95028545147843</v>
+        <v>18.86368008924605</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1.219714281949419</v>
+        <v>0.5370164477750696</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L158" s="2" t="n">
         <v>0</v>
@@ -8846,31 +8846,31 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>-0.0043629020471246</v>
+        <v>0.5377277803078179</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>3004</v>
+        <v>2547</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>豐達科</t>
+          <t>日勝生</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>404.9333642784369</v>
+        <v>403.5806929635449</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>120</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8881,16 +8881,16 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>48.88690679144142</v>
+        <v>49.26992593897748</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>18.86368008262028</v>
+        <v>13.5241818215199</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.5370164477750696</v>
+        <v>0.5225903882937775</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>0</v>
@@ -8899,31 +8899,31 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.5377277813893985</v>
+        <v>0.0215458457469224</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>2547</v>
+        <v>3018</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>日勝生</t>
+          <t>隆銘綠能</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>403.5806929635449</v>
+        <v>397.6788195358175</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -8934,16 +8934,16 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>49.2699257864909</v>
+        <v>30.64043919840221</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>13.52418182320936</v>
+        <v>14.81644748733565</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.5225903882937775</v>
+        <v>5.297607769100294</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L160" s="2" t="n">
         <v>0</v>
@@ -8952,31 +8952,31 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.0215458457829747</v>
+        <v>-0.1065743510387122</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>3018</v>
+        <v>2538</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>隆銘綠能</t>
+          <t>基泰</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>397.6788195358175</v>
+        <v>397.3258412348196</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>10.35</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8987,16 +8987,16 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>30.64043920507619</v>
+        <v>52.61971352439331</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>14.81644764746046</v>
+        <v>25.78911779406432</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>5.297607769100294</v>
+        <v>0.3053029793523372</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L161" s="2" t="n">
         <v>0</v>
@@ -9005,31 +9005,31 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-0.106574350942574</v>
+        <v>0.04288249164642</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>2538</v>
+        <v>2459</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>基泰</t>
+          <t>敦吉</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>397.3258412348196</v>
+        <v>396.2692151700786</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -9040,13 +9040,13 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>52.61971328241378</v>
+        <v>46.07803220088353</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>25.78911784842426</v>
+        <v>15.12947107030303</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.3053029793523372</v>
+        <v>1.074227488323794</v>
       </c>
       <c r="K162" s="2" t="n">
         <v>0</v>
@@ -9058,31 +9058,31 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.0428824916944884</v>
+        <v>0.0372893146402131</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>2459</v>
+        <v>2905</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>敦吉</t>
+          <t>三商</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>396.2692151700786</v>
+        <v>392.3304291669144</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>65.2</v>
+        <v>17.45</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9093,13 +9093,13 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>46.0780317918841</v>
+        <v>41.52659257338802</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>15.12947090774284</v>
+        <v>18.5026535166287</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>1.074227488323794</v>
+        <v>0.9418575042082976</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>0</v>
@@ -9111,31 +9111,31 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>0.0372893149045984</v>
+        <v>-0.1403281494108212</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>2905</v>
+        <v>2812</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>三商</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>392.3304291669144</v>
+        <v>389.3068656230753</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>17.45</v>
+        <v>18.6</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9146,13 +9146,13 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>41.52659242229856</v>
+        <v>38.15957913858843</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>18.50265346270696</v>
+        <v>20.74970348792276</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.9418575042082976</v>
+        <v>1.012376235222068</v>
       </c>
       <c r="K164" s="2" t="n">
         <v>0</v>
@@ -9164,31 +9164,31 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-0.1403281493867869</v>
+        <v>-0.0353974791651093</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>2812</v>
+        <v>2486</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>一詮</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>389.3068656230755</v>
+        <v>388.2572070362738</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>18.6</v>
+        <v>219.5</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9199,13 +9199,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>38.15957888355244</v>
+        <v>35.67002644434048</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>20.74970353062469</v>
+        <v>22.0317905989268</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>1.012376235222068</v>
+        <v>1.468829223505355</v>
       </c>
       <c r="K165" s="2" t="n">
         <v>0</v>
@@ -9217,31 +9217,31 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.0353974791410757</v>
+        <v>-1.304513273127859</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>2486</v>
+        <v>3022</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>一詮</t>
+          <t>威強電</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>388.2572070362738</v>
+        <v>387.5752860569012</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>219.5</v>
+        <v>89</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9252,49 +9252,49 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>35.67002642131419</v>
+        <v>45.51358663264211</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>22.03179039643923</v>
+        <v>15.83331182227162</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>1.468829223505355</v>
+        <v>0.6162131528858098</v>
       </c>
       <c r="K166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L166" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M166" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-1.304513272502962</v>
+        <v>-0.1174822459449473</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>3022</v>
+        <v>2474</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>威強電</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>387.5752860569012</v>
+        <v>386.2787142800179</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9305,49 +9305,49 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>45.51358659117106</v>
+        <v>30.05141060849824</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>15.83331179114577</v>
+        <v>20.71178317514929</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.6162131528858098</v>
+        <v>0.6478349529292872</v>
       </c>
       <c r="K167" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L167" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M167" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.1174822458968832</v>
+        <v>-1.84854057733003</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>2474</v>
+        <v>2535</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>386.2787142800179</v>
+        <v>385.0216168543854</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>194</v>
+        <v>89</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -9358,69 +9358,69 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>30.0514106789584</v>
+        <v>47.12979917360762</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>20.71178316033593</v>
+        <v>12.32195510484588</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.6478349529292872</v>
+        <v>1.723282828133781</v>
       </c>
       <c r="K168" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-1.84854057733003</v>
+        <v>0.08683310312719821</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>2535</v>
+        <v>2809</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>京城銀</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>385.0216168543851</v>
+        <v>370.7436807359165</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>89</v>
+        <v>56.6</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="G169" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>47.12979922203027</v>
+        <v>46.26955152455823</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>12.32195496600472</v>
+        <v/>
       </c>
       <c r="J169" s="2" t="n">
-        <v>1.723282828133781</v>
+        <v>6.141559236203543</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L169" s="2" t="n">
         <v>0</v>
@@ -9429,11 +9429,11 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0.0868331031031455</v>
+        <v>0.06437202925089371</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>369.8100706271189</v>
+        <v>369.8100706271191</v>
       </c>
       <c r="E170" s="2" t="n">
         <v>20.8</v>
@@ -9464,10 +9464,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>46.1815431087778</v>
+        <v>46.18154305008626</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>15.40440905128482</v>
+        <v>15.40440927747857</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>1.322964600558309</v>
@@ -9517,10 +9517,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>43.52665830196031</v>
+        <v>43.52665820249718</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>20.40651357367196</v>
+        <v>20.40651363101242</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.6251617030858259</v>
@@ -9535,7 +9535,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.0583875887412018</v>
+        <v>-0.0583875886931347</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>367.7464807300584</v>
+        <v>367.7464807300585</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>10.9</v>
@@ -9570,10 +9570,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>37.13013070759715</v>
+        <v>37.13013086127219</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>13.49907717425544</v>
+        <v>13.49907705752171</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>1.124255258958281</v>
@@ -9588,7 +9588,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-0.0395136826595853</v>
+        <v>-0.0395136826836203</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>366.7197771895651</v>
+        <v>366.719777189565</v>
       </c>
       <c r="E173" s="2" t="n">
         <v>51.5</v>
@@ -9623,10 +9623,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>31.38862870340338</v>
+        <v>31.38862893134305</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>11.93038727850854</v>
+        <v>11.93038745566369</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>1.92671868536244</v>
@@ -9641,7 +9641,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.094235746173394</v>
+        <v>-0.0942357464618085</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9676,10 +9676,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>52.04069629338145</v>
+        <v>52.04069643029583</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>13.86186444564948</v>
+        <v>13.86186444705228</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.8848409889218327</v>
@@ -9694,7 +9694,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>0.0290765799554394</v>
+        <v>0.0290765799193839</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9729,10 +9729,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>35.43518427312762</v>
+        <v>35.43518411428332</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>21.74920303307892</v>
+        <v>21.74920333460517</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>1.135354099281204</v>
@@ -9747,7 +9747,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-0.1245066748414704</v>
+        <v>-0.1245066747453322</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>364.1210608577238</v>
+        <v>364.1210608577237</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>20.35</v>
@@ -9782,10 +9782,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>31.01894181156719</v>
+        <v>31.01894187517568</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>21.41146508641564</v>
+        <v>21.41146502955135</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>0.6853648964051531</v>
@@ -9800,7 +9800,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-0.033632534712766</v>
+        <v>-0.033632534736802</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>354.3216061299055</v>
+        <v>354.3216061299053</v>
       </c>
       <c r="E177" s="2" t="n">
         <v>8.220000000000001</v>
@@ -9835,10 +9835,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>37.99209152255162</v>
+        <v>37.99209156908255</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>13.36908128408926</v>
+        <v>13.36908126527475</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>1.104328264528301</v>
@@ -9888,10 +9888,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>39.95324777802801</v>
+        <v>39.95324788198427</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>21.08664111784542</v>
+        <v>21.08664129709803</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>0.9962479420177672</v>
@@ -9906,7 +9906,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-0.1899722690243007</v>
+        <v>-0.1899722694088421</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>348.141962854189</v>
+        <v>348.1419628541889</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>51.9</v>
@@ -9941,10 +9941,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>43.1142242499451</v>
+        <v>43.11422448781394</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>17.15499068667364</v>
+        <v>17.15499084542235</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>0.7619031702327084</v>
@@ -9959,7 +9959,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.0768104120500647</v>
+        <v>-0.0768104126028617</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>347.472979640966</v>
+        <v>347.4729796409642</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>163</v>
@@ -9997,7 +9997,7 @@
         <v>38.22701171213127</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>13.52026223417103</v>
+        <v>13.52026226867242</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.708274210967375</v>
@@ -10012,7 +10012,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.5839236056550211</v>
+        <v>-0.5839236057752074</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10047,10 +10047,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>48.6419608715692</v>
+        <v>48.64196091189456</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>19.19413172615566</v>
+        <v>19.19413174714133</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>1.005014683742588</v>
@@ -10065,7 +10065,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-0.0553998221308336</v>
+        <v>-0.0553998221548512</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10100,10 +10100,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>33.08480917252803</v>
+        <v>33.08480921933872</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>17.55462672601249</v>
+        <v>17.55462663379674</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>5.542009483139257</v>
@@ -10118,7 +10118,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.119348811453688</v>
+        <v>-0.1193488114657054</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>336.9268003158613</v>
+        <v>336.9268003158616</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>33.35</v>
@@ -10153,10 +10153,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>36.74550816633834</v>
+        <v>36.74550858769307</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>21.2581654016777</v>
+        <v>21.25816556517305</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.8757921799484535</v>
@@ -10171,7 +10171,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>0.0494038503643291</v>
+        <v>0.0494038498836397</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10206,10 +10206,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>53.30446458116038</v>
+        <v>53.3044646531352</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>36.07618586917116</v>
+        <v>36.07618592076828</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>0.2790348907193934</v>
@@ -10224,7 +10224,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.2096889665306527</v>
+        <v>-0.2096889666988977</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>324.4814892381128</v>
+        <v>324.4814892381122</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>22.8</v>
@@ -10259,10 +10259,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>43.12730597125913</v>
+        <v>43.12730596387679</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>24.05939139844727</v>
+        <v>24.05939131633389</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>0.7439350906683032</v>
@@ -10277,7 +10277,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.0379884541739632</v>
+        <v>0.0379884541859781</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>322.9529924728179</v>
+        <v>322.9529924728196</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>13.1</v>
@@ -10312,7 +10312,7 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>33.04271525717387</v>
+        <v>33.04271548114127</v>
       </c>
       <c r="I186" s="2" t="n">
         <v>12.86311242118371</v>
@@ -10330,7 +10330,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.008387091950325901</v>
+        <v>-0.008387091974359599</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>39.65503621071023</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>30.63642579957272</v>
+        <v>30.63642597235925</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>1.290692521891507</v>
@@ -10404,7 +10404,7 @@
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>317.1938336561901</v>
+        <v>317.1938336561902</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>5.73</v>
@@ -10418,10 +10418,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>48.2332795076046</v>
+        <v>48.23327977615185</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>13.27041247235358</v>
+        <v>13.27041248357656</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>1.479325555144051</v>
@@ -10436,7 +10436,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-0.0075451442204215</v>
+        <v>-0.0075451442420522</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>316.15382135435</v>
+        <v>316.1538213543524</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>18.6</v>
@@ -10471,10 +10471,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>50.80773440125036</v>
+        <v>50.80773462495337</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>32.61693042838517</v>
+        <v>32.61693043984482</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.3261179470419939</v>
@@ -10489,7 +10489,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.0763934423243772</v>
+        <v>-0.0763934426368265</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>312.1445630497236</v>
+        <v>312.1445630497226</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>16.55</v>
@@ -10524,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>39.51791971368418</v>
+        <v>39.51792014598276</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>12.47563244405928</v>
+        <v>12.47563230342213</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>1.076257105864179</v>
@@ -10542,7 +10542,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.0186023474155967</v>
+        <v>-0.0186023475598046</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>310.5289130363591</v>
+        <v>310.5289130363587</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>22</v>
@@ -10577,10 +10577,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>46.74116015438814</v>
+        <v>46.7411604382587</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>17.19343598693538</v>
+        <v>17.19343610348687</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>1.012520320233489</v>
@@ -10595,7 +10595,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.0653121272929942</v>
+        <v>0.0653121270286157</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10630,10 +10630,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>48.35138791790072</v>
+        <v>48.35138803379724</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>15.04726299113843</v>
+        <v>15.04726294982933</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>1.07406107231578</v>
@@ -10648,7 +10648,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>0.2489344300353522</v>
+        <v>0.2489344299151789</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10683,10 +10683,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>37.39406077774619</v>
+        <v>37.39406086482796</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>18.35645772678602</v>
+        <v>18.35645781392638</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>1.0115222343465</v>
@@ -10701,7 +10701,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.09535401821822059</v>
+        <v>-0.0953540182662823</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>301.838983365557</v>
+        <v>301.8389833655572</v>
       </c>
       <c r="E194" s="2" t="n">
         <v>77.90000000000001</v>
@@ -10739,7 +10739,7 @@
         <v>35.12626535718995</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>15.73751606285416</v>
+        <v>15.73751607422047</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>1.099609580438186</v>
@@ -10754,7 +10754,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.0144626356401311</v>
+        <v>-0.0144626357603137</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10789,10 +10789,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>42.11061845700481</v>
+        <v>42.11061857524344</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>18.31384835457181</v>
+        <v>18.31384853257105</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>0.7187475801447053</v>
@@ -10807,7 +10807,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.07923702921412989</v>
+        <v>-0.07923702927181391</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>38.979679972399</v>
+        <v>38.97967995476588</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>15.2698755414226</v>
+        <v>15.26987557146043</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>1.011442156419289</v>
@@ -10860,7 +10860,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.0021809243461084</v>
+        <v>0.002180924298039</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>290.3527313036126</v>
+        <v>290.3527313036127</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>8.029999999999999</v>
@@ -10895,7 +10895,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>51.19474516123873</v>
+        <v>51.19474517565305</v>
       </c>
       <c r="I197" s="2" t="n">
         <v>4.38450777569993</v>
@@ -10913,7 +10913,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.0517040160006924</v>
+        <v>-0.0517040160247266</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10948,10 +10948,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>40.71910234686758</v>
+        <v>40.71910243824743</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>10.29133573623042</v>
+        <v>10.29133565904873</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>1.191924167716865</v>
@@ -11001,10 +11001,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>42.29030858874612</v>
+        <v>42.29030874165218</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>18.75187311340096</v>
+        <v>18.75187322506367</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.7910866037662464</v>
@@ -11019,7 +11019,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.0677153421487018</v>
+        <v>-0.0677153423049305</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>284.5313519627249</v>
+        <v>284.5313519627251</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>13.65</v>
@@ -11054,10 +11054,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>42.25495699238228</v>
+        <v>42.25495718553213</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>10.63826360070634</v>
+        <v>10.63826345637589</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>0.5950414639881301</v>
@@ -11072,7 +11072,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.0189420390085549</v>
+        <v>-0.0189420391287278</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>284.1105195312517</v>
+        <v>284.1105195312516</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>31.45</v>
@@ -11107,10 +11107,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>29.63461987710509</v>
+        <v>29.63462005303863</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>12.57732848045531</v>
+        <v>12.5773284263378</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>1.138714853467762</v>
@@ -11125,7 +11125,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.1673273034668811</v>
+        <v>-0.1673273040917779</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11160,10 +11160,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>44.63557636717218</v>
+        <v>44.63557639444478</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>22.47907581270072</v>
+        <v>22.47907583602971</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.9560361757402144</v>
@@ -11178,7 +11178,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.1338051057048174</v>
+        <v>0.1338051056327163</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>279.9228311858798</v>
+        <v>279.9228311858797</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>56.5</v>
@@ -11213,10 +11213,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>35.30510250552716</v>
+        <v>35.30510261875617</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>15.21073727445368</v>
+        <v>15.21073739551448</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.930783200356655</v>
@@ -11231,7 +11231,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.0702677799319571</v>
+        <v>-0.07026778034054131</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11266,10 +11266,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>38.48112844183184</v>
+        <v>38.48112845193719</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>18.85173123905018</v>
+        <v>18.85173113097053</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.7233804728235883</v>
@@ -11284,7 +11284,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.4843582343015943</v>
+        <v>-0.4843582340011603</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11319,10 +11319,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>41.6971744240545</v>
+        <v>41.69717446650188</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>15.73031989750441</v>
+        <v>15.73031987161846</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.8006234673946303</v>
@@ -11337,7 +11337,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.0846106647154681</v>
+        <v>-0.0846106646914344</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>268.2792094730243</v>
+        <v>268.2792094730237</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>14.95</v>
@@ -11372,10 +11372,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>37.11091009837536</v>
+        <v>37.11091020471796</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>26.19714159118744</v>
+        <v>26.19714158927751</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.8792952359949626</v>
@@ -11390,7 +11390,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.094742028225337</v>
+        <v>-0.0947420282672914</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>259.0421680276306</v>
+        <v>259.0421680276241</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>19.95</v>
@@ -11425,10 +11425,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>39.12066669289801</v>
+        <v>39.12066568575793</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>9.793580328273528</v>
+        <v>9.793580327042658</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>1.533422420947192</v>
@@ -11443,7 +11443,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.0280101394171766</v>
+        <v>-0.0280101388163093</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11478,10 +11478,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>41.70798974071927</v>
+        <v>41.70798986181765</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>22.5024592163956</v>
+        <v>22.50245935990774</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.5804995283367216</v>
@@ -11496,7 +11496,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.0217870300956376</v>
+        <v>-0.0217870301299637</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>249.7303637465898</v>
+        <v>249.73036374659</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>20.3</v>
@@ -11531,10 +11531,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>48.45874714050501</v>
+        <v>48.45874723961891</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>15.75983049684748</v>
+        <v>15.75983051673705</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>1.223188623316198</v>
@@ -11549,7 +11549,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.0073770304043969</v>
+        <v>0.0073770303923801</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>248.2608156145343</v>
+        <v>248.2608156145428</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>39.65</v>
@@ -11584,10 +11584,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>28.39656335759524</v>
+        <v>28.39656351704299</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>21.03155985639651</v>
+        <v>21.03155989422413</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>1.878057832986679</v>
@@ -11602,7 +11602,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>-0.3033191514156654</v>
+        <v>-0.3033191517401361</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45.16319323020036</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>13.63471107302024</v>
+        <v>13.63471101437609</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.8593326322539927</v>
@@ -11676,7 +11676,7 @@
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>240.6822080479183</v>
+        <v>240.682208047919</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>39.45</v>
@@ -11690,10 +11690,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>50.24272931856144</v>
+        <v>50.24272934269441</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>6.12040943359021</v>
+        <v>6.120409318192866</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.7966544778357144</v>
@@ -11708,7 +11708,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.0075995592458457</v>
+        <v>0.0075995591857622</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11743,10 +11743,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>29.86601466885931</v>
+        <v>29.86601474222093</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>19.90649321408897</v>
+        <v>19.90649335954721</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>1.299101249087099</v>
@@ -11761,7 +11761,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.3100306143102493</v>
+        <v>-0.3100306144304244</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11796,10 +11796,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>32.92220195486141</v>
+        <v>32.9222020061721</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>16.32387154250475</v>
+        <v>16.32387148140529</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.8847502619155745</v>
@@ -11814,7 +11814,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-0.06337914655469599</v>
+        <v>-0.06337914663881521</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>215.6764663911553</v>
+        <v>215.6764663911534</v>
       </c>
       <c r="E215" s="2" t="n">
         <v>44.2</v>
@@ -11849,10 +11849,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>28.92269569349406</v>
+        <v>28.92269579820216</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>12.81465489898049</v>
+        <v>12.81465524914945</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.8829502725264976</v>
@@ -11867,7 +11867,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.1188918015514739</v>
+        <v>-0.1188918018639288</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>213.2376971782425</v>
+        <v>213.2376971782426</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>12.05</v>
@@ -11902,10 +11902,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>46.26273816761126</v>
+        <v>46.26273837841669</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>12.30669481530054</v>
+        <v>12.30669516777469</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.7604658414153929</v>
@@ -11920,7 +11920,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.0139161948908726</v>
+        <v>-0.0139161949269247</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>21.49489196275064</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>33.30357019365244</v>
+        <v>33.30357021823788</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.5570159701808867</v>
@@ -11973,7 +11973,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.4052093712489674</v>
+        <v>-0.4052093712249319</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -12008,10 +12008,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>46.76936838054066</v>
+        <v>46.76936867342679</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>18.20693517854448</v>
+        <v>18.20693512845555</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.829265744736908</v>
@@ -12026,7 +12026,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.001112375122206</v>
+        <v>-0.0011123751822938</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>177.7798189603885</v>
+        <v>177.779818960389</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>76</v>
@@ -12061,10 +12061,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>44.3321167663058</v>
+        <v>44.33211691680899</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>18.43753002045566</v>
+        <v>18.4375299847427</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.5517835762765692</v>
@@ -12079,7 +12079,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.0675960219404933</v>
+        <v>-0.0675960227816928</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12114,10 +12114,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>29.4549153051866</v>
+        <v>29.45491539974876</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>22.92973053338093</v>
+        <v>22.92973050006293</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>1.063805411147574</v>
@@ -12132,7 +12132,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.0936404896022254</v>
+        <v>-0.093640489734413</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>160.8578855576527</v>
+        <v>160.857885557654</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>19.2</v>
@@ -12167,10 +12167,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>40.8974836867087</v>
+        <v>40.89748391815565</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>19.81444442638804</v>
+        <v>19.81444447237274</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>2.265549901551238</v>
@@ -12185,7 +12185,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.0222040483142061</v>
+        <v>-0.0222040483622753</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
